--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:56:24+00:00</t>
+    <t>2026-09-21T13:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T13:38:34+00:00</t>
+    <t>2026-09-22T07:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T07:55:38+00:00</t>
+    <t>2026-09-22T08:01:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T08:01:04+00:00</t>
+    <t>2026-09-22T08:07:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T08:07:02+00:00</t>
+    <t>2026-09-22T09:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,7 +617,7 @@
 </t>
   </si>
   <si>
-    <t>Section Points de Vigilances non codé</t>
+    <t>Section Points de Vigilances</t>
   </si>
   <si>
     <t>fr-lm-patient-summary-document.functionalStatus</t>

--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T09:47:29+00:00</t>
+    <t>2026-09-22T12:54:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:54:22+00:00</t>
+    <t>2026-09-22T12:56:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
